--- a/outputs/llm_eval/test_yjx/sig/GeneralPublic_correlation_results.xlsx
+++ b/outputs/llm_eval/test_yjx/sig/GeneralPublic_correlation_results.xlsx
@@ -417,13 +417,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.182024130304304</v>
+        <v>0.2384836831143947</v>
       </c>
       <c r="C2">
-        <v>0.2491889250331632</v>
+        <v>0.2591354204432634</v>
       </c>
       <c r="D2">
-        <v>0.1711220921910956</v>
+        <v>0.2296201402423456</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -431,13 +431,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.3146922134464517</v>
+        <v>0.308216257963934</v>
       </c>
       <c r="C3">
-        <v>0.3356564798098295</v>
+        <v>0.3563471196644992</v>
       </c>
       <c r="D3">
-        <v>0.277025537663096</v>
+        <v>0.2878606242860554</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -445,13 +445,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>0.2524836182756251</v>
+        <v>0.3391539884690698</v>
       </c>
       <c r="C4">
-        <v>0.3114282568338626</v>
+        <v>0.3718909494825127</v>
       </c>
       <c r="D4">
-        <v>0.2177471413192403</v>
+        <v>0.3003786579384557</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -459,13 +459,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>0.4057508801121634</v>
+        <v>0.4072182307652545</v>
       </c>
       <c r="C5">
-        <v>0.412946365962816</v>
+        <v>0.4175797355452078</v>
       </c>
       <c r="D5">
-        <v>0.3431349004249153</v>
+        <v>0.3554668218776117</v>
       </c>
     </row>
   </sheetData>
